--- a/import_database_app_ahcc copy.xlsx
+++ b/import_database_app_ahcc copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trenaldyikkyuarifin/Documents/Project WEB/ahcc-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976E2560-0C1A-B349-AB4F-8739A4E6B59A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0475B1-BBEE-3147-99B2-4BD62647B810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16820" xr2:uid="{5B2ED06F-61F0-3741-B7B2-9A9CA53F1BA1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17113" uniqueCount="3706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17865" uniqueCount="3851">
   <si>
     <t>Online Search - Web</t>
   </si>
@@ -11157,6 +11157,441 @@
   </si>
   <si>
     <t>CA NASOFARING T3N2Mx</t>
+  </si>
+  <si>
+    <t>Safa Chalisa Maulana Putri, Nn</t>
+  </si>
+  <si>
+    <t>anemia de fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien rawat inap dr. Niken di RSAH (WOD). Konsultasi post ranap, saat ini pasien dengan keluhan sakit perut. Konsultasi jika ada keluhan </t>
+  </si>
+  <si>
+    <t>Rudy Hermanto, Tn</t>
+  </si>
+  <si>
+    <t>Observasi</t>
+  </si>
+  <si>
+    <t>Pasien mengetahui AHCC dari keluarga, beliau konsultasi terkait hasil lab yang leokositnya naik. Sebelumnya pasien melakukan General Check up di Sunway dan sudah diberikan antibiotik. Pasien disarankan untuk cek lab dan konsultasi -+ di pertengahan bulan feb 2026</t>
+  </si>
+  <si>
+    <t>Aries Atmoko, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nodule mass di hati </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya sudah melakukan konsultasi dan melakukan USG Abdomen dengan dr. Johannes Indarandi, Sp.PD (RKZ). Pasien second opini dengan Prof ugoseno, oleh Prof Ugroseno di sarankan untuk melakukan CT Scan Abdomen. </t>
+  </si>
+  <si>
+    <t>Ahmad Fanani, S.AGM.PD.I, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari Keluarga, beliau sebelumnya sudah melakukan biopsi di Graha Amarta dengan dr. Bakti Surarso, SP.THT dan disarankan untuk melakukan operasi. Pasien second opini dengan dr. Dyah erawati, tetap disarankan untuk melakukan operasi terlebih dahulu. Untuk pengobatan selanjutnya mengikuti hasil operasi dengan dr. Bakti Surarso. </t>
+  </si>
+  <si>
+    <t>Ong Tonny Onggo, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB (Konsultasi tanpa pasien), beliau sebelumnya adalah pasien Prof Ugroseno dan dr. Pangestue Adi di RS Darmo. Pasien menolak melakukan BMA dan meminta pulang saat ranap di Darmo. Pasien saat ini ranap di RS Kemenkes di rawat oleh dr. Nina Oktafianti Marfu'Ah, Sp.PD. Saat ini pasien sudah melakukan kemoterapi di AHCC. </t>
+  </si>
+  <si>
+    <t>Surya Atmadinata, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari Dr. Lee Yuh Shan (Gleneagles Hospital) - tanpa rujukan (WOD) . Beliau sebelumnya dirawat oleh Prof. Dr. dr. Ami Ashariati, Sp.PD-KHOM, FINASIM (Siloam) dan sudah melakukan Kemoterapi. Kondisi pasien menurun, oleh keluarga pasien di bawa untuk konsultasi di Gleneagles Hospital dan diberikan obat Calquence. Oleh Dr. Lee Yuh Shan diberikan saran untuk melakukan konsultasi dengan dr. Niken. Konsultasi 2 minggu lagi dengan membawa hasil lab yang terbaru. </t>
+  </si>
+  <si>
+    <t>Sri Fatmawati, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya dirawat dr. Pungky Mulawardhana, Sp.OG(K)Onk (RSOS) dan sudah melakukan operasi TAH BSO. Oleh dr. Pungky Mulawardhana, Sp.OG(K)Onk disarankan untuk melakukan kemoterapi, pasien second opini dengan dr. Primadono. Oleh dr. Primadono tetp disarankan untuk melakukan kemoterapi. Pasien berunding. </t>
+  </si>
+  <si>
+    <t>Boediharto Kartyasa, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Tomy Lesmana, Sp.B, Subsp.BD (K) (Graha Amarta). Pasien sebelumnya di rawat di RSAL selama 2 minggu tanpa tegak diagnosa, pasien pindah di Graha Amarta dirawat oleh dr. Tomy Lesmana, Sp.B, Subsp.BD (K). Beliau sudah melakukan operasi di Graha Amarta, untuk radiasi pasien masih berunding dan berencana second opini di RS Mitra Keluarga Kenjeran. </t>
+  </si>
+  <si>
+    <t>Sugiharto, Tn</t>
+  </si>
+  <si>
+    <t>ca brain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dr. Rahadian Indarto Susilo, Sp.BS (RS Premier Surabaya). Beliau post operasi dengan dr. Rahadian Indarto Susilo, Sp.BS di premier Surabaya, dan disarankan untuk melakukan Radiasi. Saat ini pasien penjadwalan (Asuransi SunLife) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lina Sonyate, Ny </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya mengeluhkan pusing 1 bulan lebih, dan sudah minum obat dari dr. umum tapi tidak membaik. Pasien disarankan untuk rawat inap </t>
+  </si>
+  <si>
+    <t>Maria Ulfah, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pasien mendapatkan rujukan dari dr. Yoke, Sp. Rad (K) Onk di Graha Amarta, beliau sebelumnya sudah melakukan operasi di Mayapada dengan (dr. Nina Irawati, Sp.B (K) Onk).  Pasien belum disarankan untuk melakukan Kemoterapi, saat ini pasien sudah melakukan radiasi di AHCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Ulfah, Ny (UY) (Ca Mammae) () Pasien Prof Ugroseno di Mayapada (WOD), beliau hanya konsultasi hasil CT Simulator dengan dr. Yoke. Oeh Prof Ugroseno di sarankan untuk konsultasi setelah radiasi selesai.  </t>
+  </si>
+  <si>
+    <t>Michael Shawn Hartanto, An</t>
+  </si>
+  <si>
+    <t>limfadenopati coli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rekomendasi dari dr. Stephani Linggawan, Sp. THT-KL (WOD) tanpa rujukan, beliau datang dengan keluhan benjolan di area leher dan belum ada pemeriksaan apapun. Oleh dr. Niken disarankan untuk melakukan USG KGB dan konsultasi rencana biopsi dengan dr. Dwi hari Susilo (RSOS) </t>
+  </si>
+  <si>
+    <t>Yurike Florensia Linarwan, Nn</t>
+  </si>
+  <si>
+    <t>Pasien mendapatkan rujukan dari dr. Bob J. Octovianus, Sp.B, MCH., FICS (RSOS), Beliau sudah melakukan operasi dan belum disarankan untuk melakukan Kemoterapi. Saat ini pasien sudah melakukan radiasi di AHCC (Prudential)</t>
+  </si>
+  <si>
+    <t>Slamet Harianto, Tn</t>
+  </si>
+  <si>
+    <t>susp. Hepatoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Rustiadji, Sp. R (Klinik Pribadi Surabaya), beliau mengeluhkan nyeri pungguh selama 3 bulan tidak ada perubahan. Beliau sudah melakukan USG. Oleh Prof Ugroseno disarankan untuk USG Abdomen dan konsultasi di tanggal 20/01 </t>
+  </si>
+  <si>
+    <t>Hafeez Utsman Makky, An</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB (Konsul Tele), beliau sebelumnya sudah melakukan BMA di RSUD Sardjito dan belum ada tegak diagnosanya. Oleh dr. Shinta disarankan untuk konsultasi kedatangan ke Surabaya karena pasien berdomisili Surakarta. </t>
+  </si>
+  <si>
+    <t>Mathuri,Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Antonius Harijanto Widjaja, Sp.THT-KL (AMC - RSAH), beliau sebelumnya adalah pasien dr. Stephani Linggawan, Sp. THT-KL di AMC dan beliau sedang cuti, untuk pemeriksaan lanjutan dengan dr. Antonius Harijanto Widjaja, Sp.THT-KL. Saat ini pasien sudah melakukan radiasi di AHCC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cahyadi Yerosaka, Tn </t>
+  </si>
+  <si>
+    <t>Pasien mendapatkan rujukan dari Prof. Dr. dr. Laksmi Wulandari, Sp.P (K), FISCM, FISR (RS Darmo), sebelumnya pasien adalah pasien dari dr. Susaniwati, Sp.P (K) Onk (Mitra Keluarga Kenjeran). Pasien meminta ke dr. Susaniwati, Sp.P (K) Onk untuk di rujuk konsultasi dengan dr. Fitri Anugrah, Sp.Onk.Rad (MIKA), dan disarankan untuk melakukan radiasi paliatif sebanyak 10X3. Pasien second opini dengan Prof Laksmi dan diberikan rujukan untuk konsultasi dengan dr. Yoke di AHCC. Oleh dr. yoke disaranan untuk melakukan radiasi 10x3 (Paliatif) dan Kuratif. Fu terakhir 02/02 pasien tidak melakukan radiasi.</t>
+  </si>
+  <si>
+    <t>Pipit Puspita, Ny</t>
+  </si>
+  <si>
+    <t>Ependimoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. lulus Handayani di RSDS. Sebelumnya pasien sudah melakukan operasi 2x dengan Dr.dr. Irwan Barlian Immadoel Haq., Sp.BS (K) Onc dan tetap muncul lagi tumornya(RSDS - Menggunakan BPJS). Oleh Dr.dr. Irwan Barlian Immadoel Haq., Sp.BS (K) memberikan rujukan ke dr. Lulus Handayani di Graha Amarta. Saat ini pasien sudah melakukan radiasi di AHCC </t>
+  </si>
+  <si>
+    <t>Lanni, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca Endometrium meta colon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rekomendasi dari dr. Poedjo (Klinik pribadi - tanpa rujukan), pasien saat ini sedang rawat inap di RS National hospital dr. Tomy Lesmana, Sp.B, Subsp.BD (K) dan sudah melakukan biopsi untuk penyebaran diarea Colon dan hasil belum keluar. oleh dr. Lulus disarankan untuk menunggu hasil biopsi keluar dan konsultasi kembali. fu terakhir pasien melakukan pengobatan di Rumah sakit lain. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendra Krisbiyanto, Tn </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STS di plantar pedis kanan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya sudah melakukan operasi dengan dr. Rudy Tharry, Sp. B (K) Onk di RSUD dr. H.Jusuf SK Kalimantan Utara. Beliau disarankan untuk melakukan Radioterapi oleh dokter bedah. Oleh dr. dyah disarankan untuk menunggu luka post operasi kering, follow up di awal bulan Febriari (Fu terakhir 02 Feb belum ada jawaban) </t>
+  </si>
+  <si>
+    <t>Dwi Kusnaryanto, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien Post ranap di RSAH dengan dr. Niken, pasien konsultasi untuk menunjukan hasil lab yang terbaru. Disarankan untuk transfusi di ODC </t>
+  </si>
+  <si>
+    <t>Mariatoen Elly Kartikasari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari Dr. dr. Brahmana Askandar, Sp.OG (K)-Onk (Graha Amarta), beliau sebelumnya sudah melakukan biopsi di RS Putri dengan dr. Zettira Maulida Prasha, Sp.OG dan dinyatakan miom. Namun, beliau di berikan rujukan untuk konsultasi dengan dr. Poedjo di RSIA Putri dan disarankan untuk menunggu 3 bulan lagi untuk ct scan karena benjolan cancernya sangat kecil. Pasien second opini dengan dr. Brahmana, dan di rujuk ke dr Lulus Handayani untuk memutuskan radiasi atau tidak. Saat ini pasien sudah melakukan radiasi di AHCC </t>
+  </si>
+  <si>
+    <t>Soehardjo Partowidjojo, Tn</t>
+  </si>
+  <si>
+    <t>CA appendix metastase peritoneum</t>
+  </si>
+  <si>
+    <t>Pasien mengetahui AHCC dari dr. leli (Gleneagles Hospital), pasien sebelumnya melakukan kemoterapi, pet scan, dan biopsi di Month Elizabeth Singapore. Pasien disarankan untuk melakukan avastin di Indonesia. Beliau sudah terjadwal untuk Avastin.</t>
+  </si>
+  <si>
+    <t>Handoyo, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca pancreas </t>
+  </si>
+  <si>
+    <t>Pasien post ranap di RSAH, Konsultasi post ranap di RSAH. Beliau sebelumnya sudah melakukan pembedahan di RSUD Madiun, pasien di rawat inap di RSAH di rawat oleh dr. lucianan Kbd dan sudah diakukan endoscopy. Oleh dr. Niken disarankan cek lab 3 minggu dan konsultasi, belum ada saran kemoterapi karena usia</t>
+  </si>
+  <si>
+    <t>Irma Noviarti, Dr</t>
+  </si>
+  <si>
+    <t>SCC Plantar pedis (D) post op meta inguinal (D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya adalah pasien dr. dwi hari di RSOS. Saat ini pasien direncanakan untuk operasi, untuk radiasi akan dilakukan post operasi -+ 4 minggu setelahnya. Fu -+ di akhir bulan Feb </t>
+  </si>
+  <si>
+    <t>Sholikhah Sulastri, Hj, Ny</t>
+  </si>
+  <si>
+    <t>ca mammae meta brain meta vertebra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya dirawat oleh dr. Ari Ramadhana B. M., Sp.B, Subsp.Onk(K) (RSUD Sidoarjo) dan sudah melakukan kemoterapi 6x. Pasien di sarankan untuk melakukan Imunoterapi dan pasien second opini dengan Prof Ugroseno. Untuk imunoterapi menunggu hasil IHK terbaru, fu terakhir pengobatan di pending karena kondisi pasien menurun dan saat ini rawat inap di RSUD </t>
+  </si>
+  <si>
+    <t>Rasup Hari Adiyanto, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya pasien dr. Luciana KBD di IHC, beliau disarankan untuk melakukan operasi dan kemoterapi. Pasien second opini dengan Prof Ugroseno, rencananya akan melakukan kemoterapi di RSDS menggunakan BPJS </t>
+  </si>
+  <si>
+    <t>Liauw Debie Sintawati, Ny</t>
+  </si>
+  <si>
+    <t>ca Endometrium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Lulus Handayani, beliau direncanakan untuk melakukan kemo dan radiasi di AHCC. Saat ini penjadwalan </t>
+  </si>
+  <si>
+    <t>Sicilia, Nn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari prof ugroseno di RSOS. Pasien sudah melakukan operasi dengan dr. dwirani di RSOS. Saat ini pasien sudah melakukan kemoterapi di AHCC </t>
+  </si>
+  <si>
+    <t>Eny Yustanti, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengtahui AHCC dari WEB, beliau sebelumnya pasien sudah melakukan operasi di Ghuangzo Hospital dan disarankan untuk meakukan Radiasi. Pasien berencana untk melakukan radiasi di Surabaya, oleh dr. dyah disarankan untuk radiasi -+ 5 minggu setelah operasi. Follow up pasien -+ di pertengahan februari untuk kondisi luka post operasi </t>
+  </si>
+  <si>
+    <t>Erry Partowidjojo, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya melakukan pengobatan di Adventits Hospital dan disarankan untuk melakukan Imunoterapi. Beliau second opini dengan Prof Ugroseno dan disarankan imunoterapi menggunakan Keytruda. Follow up terakhir 2 Feb, tidak jadi melakukan imunoterapi karena kondisi pasien yang tidak memungkinkan. </t>
+  </si>
+  <si>
+    <t>Ayda Christina, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari Saudara, beliau sebelumnya sudah melakukan Mestectomy dengan dr. Bob J di RSOS dan disarankan untuk kemoterapi tapi keluarga second opini ke dr. Niken. Oleh dr. Niken tetap disarankan untuk kemoterapi dan keluarga memutuskan tidak melakukan terapi apapun. </t>
+  </si>
+  <si>
+    <t>Suminah, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Brahmana Askandar di RS IHC. Pasien disarankan untuk melakukan kemoterapi dan Radioterapi, namun pasien masih berunding. Follow up setelah lebaran (Akhir bulan Maret) </t>
+  </si>
+  <si>
+    <t>Suhadi, Tn</t>
+  </si>
+  <si>
+    <t>ca cholangio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, Beliau sebelumnya sudah melakukan operasi dengan dr. Sudjatmiko, Sp.B-KBD (RS Darmo) dan disarankan untuk kemoterapi. Pasien second opini dengan Prof Ugroseno dan disarankan untuk pemeriksaan Parafin blok di RSDS (Menggunakan BPJS) </t>
+  </si>
+  <si>
+    <t>Budi Tjahjono, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaProstat meta sacrum </t>
+  </si>
+  <si>
+    <t>Pasien mendapatkan rujukan dari dr. Edwin Ongko Raharjo, Sp.U.,MARS, beliau sebelumnya sudah melakukan operasi 2x dengan dr. Edwin dan di Picaso. Saat ini pasien disarankan untuk melakukan Radioterapi. Pasien masih berunding, fu terakhir di tanggal ? Dan akan fu kembali di tanggal 18/02</t>
+  </si>
+  <si>
+    <t>Jimmy N.K.Priatman, M.ARCH.Ir, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC melalui WEB, beliau sebelumnya sudah melakukan MRI, dan Pet Scan di NUH Hospital. Saat ini pasien sedang terapi Tragiso dan konsultasi 3 minggu </t>
+  </si>
+  <si>
+    <t>Sriliani Surbakti, S.T.,M.T,Ny</t>
+  </si>
+  <si>
+    <t>ca cervix III B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Primadono (AHCC), beliau sebelumnya sudah melakukan biopsi dengan dr. Raditya Sp.OG (RS Lavalete Malang) dan disarankan untuk kemoterapi saja, pasien second opini dengan dr. Primadono dan diberikan rujukan untuk melakukan Radioterapi dan kemoterapi. Follow up terakhir pasien masih berunding. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan mengetahui AHCC dari web,  beliau sebelumnya sudah melakukan biopsi dengan dr. Raditya Sp.OG (RS Lavalete Malang) dan disarankan untuk kemoterapi saja, pasien second opini dengan dr. Primadono dan diberikan rujukan untuk melakukan Radioterapi dan kemoterapi. Follow up terakhir pasien masih berunding. </t>
+  </si>
+  <si>
+    <t>Sari Indrawati, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDD + trombositopenia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Hendry Susilo Kawilarang, Sp.JP, FIHA (AMC), Pasien dikonsultasikan karena trombosit menurun. Diberikan pengantar cek lab dan konsultasi bulan maret </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tommy Alfan, Tn</t>
+  </si>
+  <si>
+    <t>Ca colon meta vertebra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien dr. Niken saat visite di Premier Surabaya. Pasien post operasi dengan dr. Hadi Winoto, Sp.B-KBD (Premier Surabaya) dan disarankan untuk kemoterapi. Untuk asuransi BCA - Etirta sudah acc, saat ini pasien sedang rawat inap di Premier. </t>
+  </si>
+  <si>
+    <t>Liliek Wijaya, Ny</t>
+  </si>
+  <si>
+    <t>Ca colon metastase liver, paru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien dr. Niken post ranap di RSAH, sebelumnya pasien sudah melakukan kemoterapi di Pantai Hospital. Pasien disarankan untuk melakukan kemoterapi Bevazummab dan berunding. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debby Listiyani, Ny </t>
+  </si>
+  <si>
+    <t>CA Ovarium meta KGB kaki kiri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya sudah melakukan kemoterapi dengan dr. Pungky (RSDS - Menggunakan BPJS). Untuk penyebaran diarea KGB pasien sudah melakukan kemoterapi dengan Prof Ami di Siloam Hospital. Saat ini pasien konsultasi karena pembengkakan di area kaki. Oleh dr. Niken disarankan untuk melakukan USG Doppler dan cek darah D-DIMER </t>
+  </si>
+  <si>
+    <t>Christine Siandawati Lukmanto, Ny</t>
+  </si>
+  <si>
+    <t>Pasien mendapatka rujukan dari Dr. Mastura Md Yusof (Picaso), sebelumnya pasien adalah pasien dr. Niken di RKZ dan melanjutkan pengobatan di Picaso. Pasien akan melakukan kemoterapi di RKZ</t>
+  </si>
+  <si>
+    <t>Djoko Puniman, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Antonius Harijanto Widjaja, Sp.THT-KL (AMC), saat ini pasien sudah melakukan Radioterapi dan Kemoterapi dengan dr. Niken </t>
+  </si>
+  <si>
+    <t>Pasien mendapatkan rujukan dari dr. Dyah erawati, pasien saat ini sudah melakukan radiasi dan kemoterapi.</t>
+  </si>
+  <si>
+    <t>Matius Yuwono, Tn</t>
+  </si>
+  <si>
+    <t>Sups. MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Karel Ramli. Sp.PD, FINASIM (AMC), Pasien post ranap dengan keluhan di area pencernaan (BAB menghitam). Oleh dr. Niken diberikan pengantar melakukan BMA (rencana menggunakan bpjs) </t>
+  </si>
+  <si>
+    <t>Jauw Yustinus Yanaprasetya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatka rujukan dari dr Coo (Mount elizabeth), beliau sebelumya sudah melakukan kemoterapi di Singapore dan saat ini pasien sudah melakukan kemoterapi yang pertama di 19/02 </t>
+  </si>
+  <si>
+    <t>DYAH PUSPITA SARI, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Lulus Handayani, Sp.Rad, Sp.Onk.Rad (K) (Premier Surabaya) dan Dr. dr. Brahmana Askandar, Sp.OG (K)-Onk. Beliau saat ini melakukan kemoterapi di Premier dan Radioterapi di AHCC </t>
+  </si>
+  <si>
+    <t>OKTAVIANI, Ny</t>
+  </si>
+  <si>
+    <t>Pasien mengetahui AHCC dari WEB, beliau sebelumnya sudah melakukan biopsi dengan dr. Herdhana Suwartono, Sp.OG(K)-Onk (RSUD Palu), setelah hasil keluar pasien second opini di Surabaya karena keluarga besar berada di Surabaya. Oleh dr. Primadono diberikan saran untuk melakukan kemoterapi dan diberikan pengantar untuk Radioterapi dengan dr. Dyah. Follow up terakhir pasien masih berunding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan pengantar dari dr. Primadono di AHCC, beliau sebelumnya sudah melakukan biopsi dengan dr. Herdhana Suwartono, Sp.OG(K)-Onk (RSUD Palu), setelah hasil keluar pasien second opini di Surabaya karena keluarga besar berada di Surabaya. Untuk Radioterapi masih berunding, mendapatkan biaya R. Dari keluarga menyampaikan tidak mempunyai budget pengobatan. </t>
+  </si>
+  <si>
+    <t>Teddy Lie, Tn</t>
+  </si>
+  <si>
+    <t>polisitemia vera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari Saudara, beliau konsultasi hasil MCU. Oleh dr. Niken diberikan rujukan untuk melakukan USG Abdomen (pasien berunding) </t>
+  </si>
+  <si>
+    <t>Lasmini, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, sebelumnya pasien sudah melakukan biopsi di Jember dan second opini dengan dr. Primadono. Diberikan saran untuk melakukan kemoterapi dan pasien masih berunding. </t>
+  </si>
+  <si>
+    <t>RAMLI MUHAMAD, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien ranap dr. Niken dan dr. Edwin Ongko di RSAH (WOD), beliau melakukan konsultasi online dikarenakan ada keluhan pasien lemas. Oleh dr. Niken diberikan pengantar Homecare. </t>
+  </si>
+  <si>
+    <t>Djoko Soesilo Wijaya, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengetahui AHCC dari WEB, beliau sebelumnya post Operasi Laparascopy di Malaysia (Thomson Hospital), dan disarankan untuk konsultasi dengan dokter BTKC untuk pemasangan chemoport, terakhir kondisi pasien menurun. Follow up terkait kondisi belum ada jawaban. </t>
+  </si>
+  <si>
+    <t>Helin Ratna Widuri, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mengathui AHCC dari WEB, beliau sebelumnya melakukan USG dan Mammo di RSOS (dr. Wiwin) dan FNAB di Siloam (dr. Heru). Pasien second opini di Loh Guan Lye Malaysia (dr. Teoh Mei) dan dilakukan operasi Lupektomi. Setelah operasi, pasien disarankan untuk melakukan kemoterapi dan Radioterapi. Oleh Prof Ugroseno disarankan untuk melakukan kemoterapi terlebih dahulu, untuk radioterapi menunggu setelah evaluasi kemoterapi. </t>
+  </si>
+  <si>
+    <t>ADI WIDJAJA, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca prostat meta tulang </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Edwin Ongko di tempat pribadi beliau, beliau sebelumnya melakukan pengobatan di Parkway + Singapore General Hospital, hanya terapi obat saja. Konsultasi melalui telemedicine, saat ini disarankan untuk melakukan radioterapi karena ada penyebaran di area Tulang belakang. Oleh dr. Yoke diberikan saran untuk 2 lokasi radioterapi, namun dari keluarga hanya ingin fokus diarea tulang belakang saja. Sudah diberikan penjelasan biaya, namun tidak ada respon, di telpone tidak ada jawaban. Dari keluarga mempertimbangkan usia pasien dan efek dari radiasi. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lina Sulistya Suryawati, Ny </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca sinonassal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan Dr.dr. Irwan Barlian Immadoel Haq., Sp.BS (K) Onc (National Hospital), pasien post biopsi. Oleh dr. dyah pasien disarankan untuk melakukan Pet Scan terlebih dahulu dan radiasi -+ setelah lebaran </t>
+  </si>
+  <si>
+    <t>Maria Odilia, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Brahmana di RS Premier Surabaya. Saat ini pasien sudah melakukan radiasi di AHCC </t>
+  </si>
+  <si>
+    <t>Ida Novelina Limbong, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien mendapatkan rujukan dari dr. Brahmana (Graha Amarta), beliau post operasi dan untuk kemoterapi menunggu evaluasi setelah radioterapi. Pasien saat ini masih perbaikan kondisi, untuk jadwal ct sim menunggu update dari keluarga. </t>
+  </si>
+  <si>
+    <t>Suherman, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasien post ranap di RSAH, keluhan setelah ranap Hipogilkemi. Diberikan resep obat dan konsultasi jika ada keluhan. </t>
+  </si>
+  <si>
+    <t>ca colon st.4</t>
+  </si>
+  <si>
+    <t>Pasien mengetahui AHCC dari WEB, beliau sebelumnya post operasi di RKZ (dr. Iwan Kristian). Pasien disarankan untuk melakukan cek BMA + konsul BTKV untuk pemasangan chemoport</t>
   </si>
 </sst>
 </file>
@@ -11540,7 +11975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4FA8E30-572C-844C-A12D-BF1CC41965F2}">
-  <dimension ref="A1:Z1342"/>
+  <dimension ref="A1:Z1400"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
@@ -82736,6 +83171,3063 @@
         <v>3681</v>
       </c>
     </row>
+    <row r="1343" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1343">
+        <v>79724</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>3706</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D1343" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G1343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1343" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1343" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1343" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1343" s="1">
+        <v>46027</v>
+      </c>
+      <c r="L1343" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1343" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1343" s="1"/>
+      <c r="S1343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1343" s="1"/>
+      <c r="U1343" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1343" t="s">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1344">
+        <v>59924</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>3709</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>3710</v>
+      </c>
+      <c r="D1344">
+        <v>73</v>
+      </c>
+      <c r="G1344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1344" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1344" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1344" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1344" s="1">
+        <v>46027</v>
+      </c>
+      <c r="L1344" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1344" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1344" s="1"/>
+      <c r="S1344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1344" s="1"/>
+      <c r="U1344" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1344" t="s">
+        <v>3711</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1345">
+        <v>428214</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>3712</v>
+      </c>
+      <c r="C1345" t="s">
+        <v>3713</v>
+      </c>
+      <c r="D1345">
+        <v>70</v>
+      </c>
+      <c r="G1345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1345" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1345" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1345" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1345" s="1">
+        <v>46028</v>
+      </c>
+      <c r="L1345" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1345" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1345" s="1"/>
+      <c r="S1345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1345" s="1"/>
+      <c r="U1345" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1345" t="s">
+        <v>3714</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1346">
+        <v>428213</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>3715</v>
+      </c>
+      <c r="C1346" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1346">
+        <v>54</v>
+      </c>
+      <c r="F1346" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1346" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H1346" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1346" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1346" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1346" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1346" s="1"/>
+      <c r="S1346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1346" s="1"/>
+      <c r="U1346" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1346" t="s">
+        <v>3716</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1347">
+        <v>428212</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>3717</v>
+      </c>
+      <c r="C1347" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1347">
+        <v>65</v>
+      </c>
+      <c r="G1347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1347" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1347" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1347" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1347" s="1">
+        <v>46028</v>
+      </c>
+      <c r="L1347" s="1">
+        <v>46034</v>
+      </c>
+      <c r="M1347" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1347" s="1"/>
+      <c r="S1347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1347" s="1"/>
+      <c r="U1347" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1347" t="s">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1348">
+        <v>365089</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>3719</v>
+      </c>
+      <c r="C1348" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1348">
+        <v>-16</v>
+      </c>
+      <c r="F1348" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1348" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1348" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1348" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1348" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1348" s="1">
+        <v>46029</v>
+      </c>
+      <c r="L1348" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1348" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1348" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1348" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1348" s="1"/>
+      <c r="S1348" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1348" s="1"/>
+      <c r="U1348" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1348" t="s">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1349">
+        <v>427969</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>3721</v>
+      </c>
+      <c r="C1349" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1349" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G1349" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1349" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1349" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1349" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1349" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1349" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1349" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1349" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1349" s="1">
+        <v>46029</v>
+      </c>
+      <c r="R1349" s="1"/>
+      <c r="S1349" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1349" s="1"/>
+      <c r="U1349" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1349" t="s">
+        <v>3722</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1350">
+        <v>50101</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>3723</v>
+      </c>
+      <c r="C1350" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D1350">
+        <v>65</v>
+      </c>
+      <c r="F1350" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1350" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H1350" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1350" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1350" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1350" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1350" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1350" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1350" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1350" s="1"/>
+      <c r="S1350" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1350" s="1"/>
+      <c r="U1350" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1350" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1351">
+        <v>428334</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>3725</v>
+      </c>
+      <c r="C1351" t="s">
+        <v>3726</v>
+      </c>
+      <c r="D1351">
+        <v>49</v>
+      </c>
+      <c r="F1351" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1351" s="1">
+        <v>46034</v>
+      </c>
+      <c r="H1351" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1351" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1351" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1351" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1351" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1351" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1351" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1351" s="1"/>
+      <c r="S1351" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1351" s="1"/>
+      <c r="U1351" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1351" t="s">
+        <v>3727</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1352">
+        <v>227431</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>3728</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D1352">
+        <v>30</v>
+      </c>
+      <c r="G1352" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1352" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1352" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1352" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1352" s="1">
+        <v>46034</v>
+      </c>
+      <c r="L1352" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1352" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1352" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1352" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1352" s="1"/>
+      <c r="S1352" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1352" s="1"/>
+      <c r="U1352" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1352" t="s">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1353">
+        <v>427971</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>3730</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1353" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F1353" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1353" s="1">
+        <v>46037</v>
+      </c>
+      <c r="H1353" s="1">
+        <v>46034</v>
+      </c>
+      <c r="I1353" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1353" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1353" s="1">
+        <v>46035</v>
+      </c>
+      <c r="L1353" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1353" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1353" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1353" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1353" s="1"/>
+      <c r="S1353" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1353" s="1"/>
+      <c r="U1353" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1353" t="s">
+        <v>3731</v>
+      </c>
+      <c r="W1353" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1354">
+        <v>117643</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>3733</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>3734</v>
+      </c>
+      <c r="D1354">
+        <v>17</v>
+      </c>
+      <c r="G1354" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1354" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1354" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1354" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1354" s="1">
+        <v>46036</v>
+      </c>
+      <c r="L1354" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1354" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1354" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1354" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1354" s="1"/>
+      <c r="S1354" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1354" s="1"/>
+      <c r="U1354" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1354" t="s">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1355">
+        <v>383988</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>3736</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1355">
+        <v>39</v>
+      </c>
+      <c r="F1355" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1355" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H1355" s="1">
+        <v>46037</v>
+      </c>
+      <c r="I1355" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1355" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1355" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1355" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1355" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1355" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1355" s="1"/>
+      <c r="S1355" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1355" s="1"/>
+      <c r="U1355" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1355" t="s">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1356">
+        <v>428425</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>3738</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>3739</v>
+      </c>
+      <c r="D1356">
+        <v>37</v>
+      </c>
+      <c r="G1356" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1356" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1356" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1356" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1356" s="1">
+        <v>46037</v>
+      </c>
+      <c r="L1356" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1356" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1356" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1356" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1356" s="1"/>
+      <c r="S1356" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1356" s="1"/>
+      <c r="U1356" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1356" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1357">
+        <v>428293</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>3741</v>
+      </c>
+      <c r="C1357">
+        <v>0</v>
+      </c>
+      <c r="D1357">
+        <v>2</v>
+      </c>
+      <c r="G1357" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1357" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1357" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1357" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1357" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1357" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1357" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1357" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1357" s="1"/>
+      <c r="S1357" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1357" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1357" s="1">
+        <v>46031</v>
+      </c>
+      <c r="V1357" t="s">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1358">
+        <v>275127</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>3743</v>
+      </c>
+      <c r="C1358" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1358">
+        <v>56</v>
+      </c>
+      <c r="F1358" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1358" s="1">
+        <v>46041</v>
+      </c>
+      <c r="H1358" s="1">
+        <v>46044</v>
+      </c>
+      <c r="I1358" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1358" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1358" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1358" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1358" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1358" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1358" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1358" s="1"/>
+      <c r="S1358" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1358" s="1"/>
+      <c r="U1358" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1358" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1359">
+        <v>428553</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>3745</v>
+      </c>
+      <c r="C1359" t="s">
+        <v>883</v>
+      </c>
+      <c r="D1359">
+        <v>53</v>
+      </c>
+      <c r="F1359" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1359" s="1">
+        <v>46042</v>
+      </c>
+      <c r="H1359" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1359" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J1359" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1359" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1359" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1359" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="O1359" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1359" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1359" s="1"/>
+      <c r="S1359" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1359" s="1"/>
+      <c r="U1359" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1359" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1360">
+        <v>428094</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>3747</v>
+      </c>
+      <c r="C1360" t="s">
+        <v>3748</v>
+      </c>
+      <c r="D1360">
+        <v>27</v>
+      </c>
+      <c r="F1360" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1360" s="1">
+        <v>46043</v>
+      </c>
+      <c r="H1360" s="1">
+        <v>46030</v>
+      </c>
+      <c r="I1360" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1360" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1360" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1360" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1360" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1360" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1360" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1360" s="1"/>
+      <c r="S1360" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1360" s="1"/>
+      <c r="U1360" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1360" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1361">
+        <v>388003</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>3750</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>3751</v>
+      </c>
+      <c r="D1361">
+        <v>70</v>
+      </c>
+      <c r="F1361" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1361" s="1">
+        <v>46044</v>
+      </c>
+      <c r="H1361" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1361" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J1361" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1361" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1361" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1361" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="O1361" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1361" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1361" s="1"/>
+      <c r="S1361" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1361" s="1"/>
+      <c r="U1361" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1361" t="s">
+        <v>3752</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1362">
+        <v>428629</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>3753</v>
+      </c>
+      <c r="C1362" t="s">
+        <v>3754</v>
+      </c>
+      <c r="D1362">
+        <v>38</v>
+      </c>
+      <c r="F1362" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1362" s="1">
+        <v>46045</v>
+      </c>
+      <c r="H1362" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1362" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1362" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1362" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1362" s="1"/>
+      <c r="O1362" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1362" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1362" s="1"/>
+      <c r="S1362" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1362" s="1"/>
+      <c r="U1362" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1362" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1363">
+        <v>428330</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>3756</v>
+      </c>
+      <c r="C1363" t="s">
+        <v>312</v>
+      </c>
+      <c r="D1363">
+        <v>49</v>
+      </c>
+      <c r="G1363" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1363" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1363" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1363" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1363" s="1">
+        <v>46048</v>
+      </c>
+      <c r="L1363" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1363" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1363" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1363" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1363" s="1"/>
+      <c r="S1363" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1363" s="1"/>
+      <c r="U1363" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1363" t="s">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1364">
+        <v>145056</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>3758</v>
+      </c>
+      <c r="C1364" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1364">
+        <v>51</v>
+      </c>
+      <c r="F1364" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1364" s="1">
+        <v>46048</v>
+      </c>
+      <c r="H1364" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1364" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1364" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1364" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1364" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1364" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1364" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1364" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1364" s="1"/>
+      <c r="S1364" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1364" s="1"/>
+      <c r="U1364" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1364" t="s">
+        <v>3759</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1365">
+        <v>428744</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>3760</v>
+      </c>
+      <c r="C1365" t="s">
+        <v>3761</v>
+      </c>
+      <c r="D1365">
+        <v>72</v>
+      </c>
+      <c r="F1365" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1365" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1365" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1365" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1365" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1365" s="1">
+        <v>46050</v>
+      </c>
+      <c r="L1365" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1365" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="O1365" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1365" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1365" s="1"/>
+      <c r="S1365" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1365" s="1"/>
+      <c r="U1365" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1365" t="s">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1366">
+        <v>76999</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>3763</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>3764</v>
+      </c>
+      <c r="D1366">
+        <v>79</v>
+      </c>
+      <c r="G1366" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1366" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1366" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1366" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1366" s="1">
+        <v>46050</v>
+      </c>
+      <c r="L1366" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1366" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1366" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1366" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1366" s="1"/>
+      <c r="S1366" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1366" s="1"/>
+      <c r="U1366" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1366" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1367">
+        <v>428766</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>3766</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>3767</v>
+      </c>
+      <c r="D1367">
+        <v>79</v>
+      </c>
+      <c r="F1367" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1367" s="1">
+        <v>46051</v>
+      </c>
+      <c r="H1367" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1367" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K1367" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1367" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1367" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1367" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1367" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1367" s="1"/>
+      <c r="S1367" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1367" s="1"/>
+      <c r="U1367" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1367" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1368">
+        <v>428767</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>3769</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>3770</v>
+      </c>
+      <c r="D1368">
+        <v>52</v>
+      </c>
+      <c r="G1368" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1368" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1368" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1368" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1368" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L1368" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1368" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1368" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1368" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1368" s="1"/>
+      <c r="S1368" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1368" s="1"/>
+      <c r="U1368" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1368" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1369">
+        <v>428755</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>3772</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>3305</v>
+      </c>
+      <c r="D1369">
+        <v>40</v>
+      </c>
+      <c r="G1369" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1369" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1369" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1369" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1369" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L1369" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1369" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="O1369" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1369" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1369" s="1"/>
+      <c r="S1369" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1369" s="1"/>
+      <c r="U1369" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1369" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1370">
+        <v>363441</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>3774</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>3775</v>
+      </c>
+      <c r="D1370">
+        <v>62</v>
+      </c>
+      <c r="G1370" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1370" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1370" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1370" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1370" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1370" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1370" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1370" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1370" s="1">
+        <v>46052</v>
+      </c>
+      <c r="R1370" s="1"/>
+      <c r="S1370" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1370" s="1"/>
+      <c r="U1370" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1370" t="s">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1371">
+        <v>336282</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>3777</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1371">
+        <v>43</v>
+      </c>
+      <c r="G1371" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1371" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1371" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1371" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1371" s="1">
+        <v>46051</v>
+      </c>
+      <c r="L1371" s="1">
+        <v>46044</v>
+      </c>
+      <c r="M1371" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1371" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1371" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1371" s="1"/>
+      <c r="S1371" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1371" s="1"/>
+      <c r="U1371" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1371" t="s">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1372">
+        <v>428595</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>3779</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1372" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F1372" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1372" s="1">
+        <v>46043</v>
+      </c>
+      <c r="H1372" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1372" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K1372" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1372" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1372" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1372" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1372" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1372" s="1"/>
+      <c r="S1372" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1372" s="1"/>
+      <c r="U1372" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1372" t="s">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1373">
+        <v>149981</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>3781</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1373">
+        <v>84</v>
+      </c>
+      <c r="G1373" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1373" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1373" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1373" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1373" s="1">
+        <v>46042</v>
+      </c>
+      <c r="L1373" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1373" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1373" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1373" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1373" s="1"/>
+      <c r="S1373" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1373" s="1"/>
+      <c r="U1373" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1373" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1374">
+        <v>103685</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>3783</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1374">
+        <v>81</v>
+      </c>
+      <c r="G1374" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1374" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1374" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1374" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1374" s="1">
+        <v>46057</v>
+      </c>
+      <c r="L1374" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1374" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1374" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1374" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1374" s="1"/>
+      <c r="S1374" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1374" s="1"/>
+      <c r="U1374" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1374" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1375">
+        <v>428888</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>3785</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1375">
+        <v>58</v>
+      </c>
+      <c r="F1375" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1375" s="1">
+        <v>46057</v>
+      </c>
+      <c r="H1375" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1375" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1375" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1375" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1375" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1375" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1375" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1375" s="1"/>
+      <c r="S1375" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1375" s="1"/>
+      <c r="U1375" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1375" t="s">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1376">
+        <v>428895</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>3787</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>3788</v>
+      </c>
+      <c r="D1376">
+        <v>64</v>
+      </c>
+      <c r="G1376" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1376" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1376" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1376" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1376" s="1">
+        <v>46058</v>
+      </c>
+      <c r="L1376" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1376" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1376" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1376" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1376" s="1"/>
+      <c r="S1376" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1376" s="1"/>
+      <c r="U1376" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1376" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1377">
+        <v>36123</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>3790</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>3791</v>
+      </c>
+      <c r="D1377">
+        <v>76</v>
+      </c>
+      <c r="F1377" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1377" s="1">
+        <v>46058</v>
+      </c>
+      <c r="H1377" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1377" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1377" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1377" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1377" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1377" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1377" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1377" s="1"/>
+      <c r="S1377" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1377" s="1"/>
+      <c r="U1377" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1377" t="s">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1378">
+        <v>428896</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>3793</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>632</v>
+      </c>
+      <c r="D1378">
+        <v>72</v>
+      </c>
+      <c r="G1378" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1378" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1378" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1378" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1378" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1378" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1378" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1378" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1378" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1378" s="1">
+        <v>46058</v>
+      </c>
+      <c r="T1378" s="1"/>
+      <c r="U1378" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1378" t="s">
+        <v>3794</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1379">
+        <v>428918</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>3795</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>3796</v>
+      </c>
+      <c r="D1379">
+        <v>51</v>
+      </c>
+      <c r="F1379" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1379" s="1">
+        <v>46062</v>
+      </c>
+      <c r="H1379" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1379" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1379" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1379" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1379" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1379" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1379" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1379" s="1">
+        <v>46059</v>
+      </c>
+      <c r="R1379" s="1"/>
+      <c r="S1379" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1379" s="1"/>
+      <c r="U1379" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1379" t="s">
+        <v>3797</v>
+      </c>
+      <c r="W1379" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1380">
+        <v>182814</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>3799</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>3800</v>
+      </c>
+      <c r="D1380">
+        <v>76</v>
+      </c>
+      <c r="G1380" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1380" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1380" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1380" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1380" s="1">
+        <v>46063</v>
+      </c>
+      <c r="L1380" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1380" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1380" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1380" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1380" s="1"/>
+      <c r="S1380" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1380" s="1"/>
+      <c r="U1380" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1380" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1381">
+        <v>429029</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>3802</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>3803</v>
+      </c>
+      <c r="D1381">
+        <v>48</v>
+      </c>
+      <c r="G1381" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1381" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1381" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1381" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1381" s="1">
+        <v>46064</v>
+      </c>
+      <c r="L1381" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1381" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="O1381" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1381" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1381" s="1"/>
+      <c r="S1381" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1381" s="1"/>
+      <c r="U1381" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1381" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1382">
+        <v>427259</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>3805</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>3806</v>
+      </c>
+      <c r="D1382">
+        <v>83</v>
+      </c>
+      <c r="G1382" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1382" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1382" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1382" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1382" s="1">
+        <v>46064</v>
+      </c>
+      <c r="L1382" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1382" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1382" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1382" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1382" s="1"/>
+      <c r="S1382" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1382" s="1"/>
+      <c r="U1382" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1382" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1383">
+        <v>429026</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>3808</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>3809</v>
+      </c>
+      <c r="D1383">
+        <v>65</v>
+      </c>
+      <c r="G1383" s="1">
+        <v>46069</v>
+      </c>
+      <c r="H1383" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1383" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1383" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1383" s="1">
+        <v>46064</v>
+      </c>
+      <c r="L1383" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1383" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1383" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1383" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1383" s="1"/>
+      <c r="S1383" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1383" s="1"/>
+      <c r="U1383" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1383" t="s">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1384">
+        <v>429106</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>3811</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1384">
+        <v>47</v>
+      </c>
+      <c r="G1384" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1384" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1384" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1384" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1384" s="1">
+        <v>46069</v>
+      </c>
+      <c r="L1384" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1384" s="1" t="s">
+        <v>1615</v>
+      </c>
+      <c r="O1384" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1384" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1384" s="1"/>
+      <c r="S1384" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1384" s="1"/>
+      <c r="U1384" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1384" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1385">
+        <v>281094</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>3813</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1385">
+        <v>53</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1385" s="1">
+        <v>46069</v>
+      </c>
+      <c r="H1385" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1385" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1385" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1385" s="1">
+        <v>46069</v>
+      </c>
+      <c r="L1385" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1385" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1385" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1385" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1385" s="1"/>
+      <c r="S1385" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1385" s="1"/>
+      <c r="U1385" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1385" t="s">
+        <v>3814</v>
+      </c>
+      <c r="W1385" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1386">
+        <v>67228</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>3816</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>3817</v>
+      </c>
+      <c r="D1386">
+        <v>84</v>
+      </c>
+      <c r="G1386" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1386" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1386" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1386" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1386" s="1">
+        <v>46069</v>
+      </c>
+      <c r="L1386" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1386" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O1386" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1386" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1386" s="1"/>
+      <c r="S1386" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1386" s="1"/>
+      <c r="U1386" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1386" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1387">
+        <v>429120</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>3819</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D1387">
+        <v>126</v>
+      </c>
+      <c r="G1387" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1387" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1387" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1387" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1387" s="1">
+        <v>46069</v>
+      </c>
+      <c r="L1387" s="1">
+        <v>46072</v>
+      </c>
+      <c r="M1387" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1387" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1387" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1387" s="1"/>
+      <c r="S1387" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1387" s="1"/>
+      <c r="U1387" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1387" t="s">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1388">
+        <v>428583</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>3821</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1388">
+        <v>67</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1388" s="1">
+        <v>46071</v>
+      </c>
+      <c r="H1388" s="1">
+        <v>46055</v>
+      </c>
+      <c r="I1388" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1388" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1388" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1388" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1388" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1388" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1388" s="1"/>
+      <c r="S1388" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1388" s="1"/>
+      <c r="U1388" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1388" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1389">
+        <v>429135</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>3823</v>
+      </c>
+      <c r="C1389">
+        <v>0</v>
+      </c>
+      <c r="D1389">
+        <v>41</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1389" s="1">
+        <v>46071</v>
+      </c>
+      <c r="H1389" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1389" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1389" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1389" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1389" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1389" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1389" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1389" s="1">
+        <v>46071</v>
+      </c>
+      <c r="R1389" s="1"/>
+      <c r="S1389" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1389" s="1"/>
+      <c r="U1389" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1389" t="s">
+        <v>3824</v>
+      </c>
+      <c r="W1389" t="s">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1390">
+        <v>429143</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>3826</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>3827</v>
+      </c>
+      <c r="D1390" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G1390" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1390" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1390" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1390" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1390" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L1390" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1390" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1390" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1390" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1390" s="1"/>
+      <c r="S1390" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1390" s="1"/>
+      <c r="U1390" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1390" t="s">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1391">
+        <v>429142</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>3829</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>3242</v>
+      </c>
+      <c r="D1391">
+        <v>59</v>
+      </c>
+      <c r="G1391" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1391" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1391" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1391" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1391" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1391" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1391" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1391" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1391" s="1">
+        <v>46071</v>
+      </c>
+      <c r="R1391" s="1"/>
+      <c r="S1391" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1391" s="1"/>
+      <c r="U1391" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1391" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A1392">
+        <v>406917</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>3831</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D1392">
+        <v>79</v>
+      </c>
+      <c r="G1392" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1392" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1392" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1392" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1392" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L1392" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1392" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1392" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1392" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1392" s="1"/>
+      <c r="S1392" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1392" s="1"/>
+      <c r="U1392" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1392" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1393">
+        <v>429140</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>3833</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1393" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G1393" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1393" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1393" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1393" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1393" s="1">
+        <v>46071</v>
+      </c>
+      <c r="L1393" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1393" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1393" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1393" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1393" s="1"/>
+      <c r="S1393" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1393" s="1"/>
+      <c r="U1393" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1393" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1394">
+        <v>429162</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>3835</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1394">
+        <v>49</v>
+      </c>
+      <c r="G1394" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1394" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1394" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1394" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1394" s="1">
+        <v>46072</v>
+      </c>
+      <c r="L1394" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1394" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1394" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1394" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1394" s="1"/>
+      <c r="S1394" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1394" s="1"/>
+      <c r="U1394" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1394" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1395">
+        <v>185207</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>3837</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>3838</v>
+      </c>
+      <c r="D1395">
+        <v>80</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1395" s="1">
+        <v>46072</v>
+      </c>
+      <c r="H1395" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1395" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1395" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1395" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1395" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1395" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1395" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1395" s="1"/>
+      <c r="S1395" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1395" s="1"/>
+      <c r="U1395" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1395" t="s">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1396">
+        <v>429190</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>3840</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>3841</v>
+      </c>
+      <c r="D1396">
+        <v>53</v>
+      </c>
+      <c r="F1396" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1396" s="1">
+        <v>46073</v>
+      </c>
+      <c r="H1396" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1396" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K1396" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1396" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1396" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1396" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1396" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1396" s="1"/>
+      <c r="S1396" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1396" s="1"/>
+      <c r="U1396" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1396" t="s">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1397">
+        <v>428626</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>3843</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1397">
+        <v>67</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1397" s="1">
+        <v>46076</v>
+      </c>
+      <c r="H1397" s="1">
+        <v>46062</v>
+      </c>
+      <c r="I1397" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1397" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1397" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1397" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1397" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1397" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1397" s="1"/>
+      <c r="S1397" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1397" s="1"/>
+      <c r="U1397" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1397" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1398">
+        <v>429232</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>3845</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D1398">
+        <v>56</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1398" s="1">
+        <v>46076</v>
+      </c>
+      <c r="H1398" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1398" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K1398" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1398" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1398" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1398" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1398" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1398" s="1"/>
+      <c r="S1398" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1398" s="1"/>
+      <c r="U1398" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1398" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1399">
+        <v>426012</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>3847</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D1399">
+        <v>76</v>
+      </c>
+      <c r="G1399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1399" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1399" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1399" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1399" s="1">
+        <v>46076</v>
+      </c>
+      <c r="L1399" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1399" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1399" s="1"/>
+      <c r="S1399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1399" s="1"/>
+      <c r="U1399" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1399" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1400">
+        <v>429249</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>2738</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>3849</v>
+      </c>
+      <c r="D1400">
+        <v>69</v>
+      </c>
+      <c r="G1400" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1400" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1400" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1400" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1400" s="1">
+        <v>46076</v>
+      </c>
+      <c r="L1400" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1400" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="O1400" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q1400" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1400" s="1"/>
+      <c r="S1400" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1400" s="1"/>
+      <c r="U1400" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1400" t="s">
+        <v>3850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
